--- a/reports/Debug-purgatory-20260106/For The Day (Actual)_Visits.xlsx
+++ b/reports/Debug-purgatory-20260106/For The Day (Actual)_Visits.xlsx
@@ -34,10 +34,10 @@
     <t>Purgatory Passes</t>
   </si>
   <si>
+    <t>Purgatory Comp Tickets</t>
+  </si>
+  <si>
     <t>Purgatory Tickets</t>
-  </si>
-  <si>
-    <t>Purgatory Comp Tickets</t>
   </si>
 </sst>
 </file>
@@ -445,7 +445,7 @@
         <v>46028</v>
       </c>
       <c r="C3" s="2">
-        <v>97</v>
+        <v>5</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -459,10 +459,10 @@
         <v>46028</v>
       </c>
       <c r="C4" s="2">
+        <v>258</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -473,7 +473,7 @@
         <v>46028</v>
       </c>
       <c r="C5" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>5</v>
@@ -487,7 +487,7 @@
         <v>46028</v>
       </c>
       <c r="C6" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -501,7 +501,7 @@
         <v>46028</v>
       </c>
       <c r="C7" s="2">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>5</v>
@@ -515,10 +515,10 @@
         <v>46028</v>
       </c>
       <c r="C8" s="2">
-        <v>1416</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -529,10 +529,10 @@
         <v>46028</v>
       </c>
       <c r="C9" s="2">
-        <v>5</v>
+        <v>1415</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -543,10 +543,10 @@
         <v>46028</v>
       </c>
       <c r="C10" s="2">
-        <v>258</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
